--- a/enews_robotas/sablonas.xlsx
+++ b/enews_robotas/sablonas.xlsx
@@ -3239,22 +3239,22 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SJNJ12TD0U2373741</t>
+          <t>TESTA000000000002</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>JRH36</t>
+          <t>TST02</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1Q9D77</t>
+          <t>1T2T02</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>TE204</t>
+          <t>T0002</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -3269,29 +3269,29 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>OAU289</t>
+          <t>AAA002</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SJNJ12TD5U2387571</t>
+          <t>TESTA000000000003</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>JRJ36</t>
+          <t>TST01</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1Q1H77</t>
+          <t>1T1T01</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>S3604</t>
+          <t>T0001</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>AYT599</t>
+          <t>AAA003</t>
         </is>
       </c>
     </row>
